--- a/single-table-double-entry-accounting_V10.xlsx
+++ b/single-table-double-entry-accounting_V10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lbdev/Documents/single-table-accounting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E0F672A-93CB-4D40-8F92-9EFE8D68D5B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C529FF0-9CF5-6E4D-BE80-2BA404F9E972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4360" yWindow="660" windowWidth="30200" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -490,7 +490,7 @@
         <r>
           <rPr>
             <sz val="12"/>
-            <color theme="1"/>
+            <color rgb="FF000000"/>
             <rFont val="Aptos Narrow"/>
           </rPr>
           <t>Month 2, Week 1. Weekly operations generated $1,100.00 of revenue, incurred $880.00 of transport expense, and paid a $150.00 owner draw, increasing the bank balance by $70.00.</t>
@@ -526,7 +526,7 @@
         <r>
           <rPr>
             <sz val="12"/>
-            <color theme="1"/>
+            <color rgb="FF000000"/>
             <rFont val="Aptos Narrow"/>
           </rPr>
           <t>Month 2, Week 4. Weekly operations generated $1,100.00 of revenue, incurred $880.00 of transport expense, and paid a $150.00 owner draw, increasing the bank balance by $70.00.</t>
@@ -718,7 +718,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="272">
   <si>
     <t>Positions, Income Statament and &amp; Balance Sheet</t>
   </si>
@@ -1496,6 +1496,55 @@
   </si>
   <si>
     <t>The workbook permits financial statements to be generated at any arbitrary transaction points rather than only at predefined reporting dates.</t>
+  </si>
+  <si>
+    <t>Closed-System =&gt; INFLOWS =&gt; Income =&gt; REVENUE</t>
+  </si>
+  <si>
+    <t>Closed-System =&gt; OUTFLOWS =&gt; Expense =&gt; TRANSPORT</t>
+  </si>
+  <si>
+    <t>Closed-System =&gt; INFLOWS =&gt; Capital =&gt; OWN_DRAW</t>
+  </si>
+  <si>
+    <t>Closed-System =&gt; OUTFLOWS =&gt; Asset =&gt; BANK</t>
+  </si>
+  <si>
+    <t>Closed-System =&gt; INFLOWS =&gt; Capital =&gt; PROP_CAP</t>
+  </si>
+  <si>
+    <r>
+      <t>Note:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve"> Each account is associated with a terminal path originating at the </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">root node Closed-System. The terminal path uniquely identifies the </t>
+  </si>
+  <si>
+    <t>account’s location within the recursive partition hierarchy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Parent accounts and higher-level reporting categories are </t>
+  </si>
+  <si>
+    <t>obtained through aggregation of terminal paths sharing a common prefix.</t>
+  </si>
+  <si>
+    <t>Teminal Paths. ( Transaction Matrix Columns)</t>
+  </si>
+  <si>
+    <t>and encodes the complete ancestry of the account from the root</t>
+  </si>
+  <si>
+    <t>node to the terminal  node.</t>
   </si>
 </sst>
 </file>
@@ -1506,7 +1555,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1635,6 +1684,17 @@
     <font>
       <b/>
       <sz val="30"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="20"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
     </font>
@@ -1892,7 +1952,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="155">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2274,6 +2334,8 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -2895,7 +2957,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B3:D14"/>
+  <dimension ref="B3:D23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="21.6640625" customWidth="1"/>
@@ -2930,6 +2992,9 @@
       <c r="C9" s="4" t="s">
         <v>90</v>
       </c>
+      <c r="D9" s="4" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="10" spans="2:4" ht="22" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="20" t="s">
@@ -2938,6 +3003,9 @@
       <c r="C10" s="20" t="s">
         <v>91</v>
       </c>
+      <c r="D10" s="20" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="11" spans="2:4" ht="22" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="20" t="s">
@@ -2946,6 +3014,9 @@
       <c r="C11" s="20" t="s">
         <v>92</v>
       </c>
+      <c r="D11" s="20" t="s">
+        <v>260</v>
+      </c>
     </row>
     <row r="12" spans="2:4" ht="22" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="20" t="s">
@@ -2954,6 +3025,9 @@
       <c r="C12" s="20" t="s">
         <v>93</v>
       </c>
+      <c r="D12" s="20" t="s">
+        <v>261</v>
+      </c>
     </row>
     <row r="13" spans="2:4" ht="22" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="20" t="s">
@@ -2962,6 +3036,9 @@
       <c r="C13" s="20" t="s">
         <v>94</v>
       </c>
+      <c r="D13" s="20" t="s">
+        <v>262</v>
+      </c>
     </row>
     <row r="14" spans="2:4" ht="22" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="20" t="s">
@@ -2969,6 +3046,44 @@
       </c>
       <c r="C14" s="20" t="s">
         <v>93</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" ht="27" x14ac:dyDescent="0.35">
+      <c r="B17" s="153" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" ht="27" x14ac:dyDescent="0.35">
+      <c r="B18" s="154" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" ht="27" x14ac:dyDescent="0.35">
+      <c r="B19" s="154" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" ht="27" x14ac:dyDescent="0.35">
+      <c r="B20" s="154" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" ht="27" x14ac:dyDescent="0.35">
+      <c r="B21" s="154" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" ht="27" x14ac:dyDescent="0.35">
+      <c r="B22" s="154" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" ht="27" x14ac:dyDescent="0.35">
+      <c r="B23" s="154" t="s">
+        <v>268</v>
       </c>
     </row>
   </sheetData>
